--- a/TestData/DeluxeTestData.xlsx
+++ b/TestData/DeluxeTestData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="96">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -125,151 +125,172 @@
     <t>PresetSaleItem2</t>
   </si>
   <si>
+    <t>ExistNumber</t>
+  </si>
+  <si>
     <t>TC_11013</t>
   </si>
   <si>
     <t>Sale</t>
   </si>
   <si>
+    <t>5/13 ZENTRO PROD TEST</t>
+  </si>
+  <si>
+    <t>umesh</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>umeshtest@testingxperts.com</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>4444</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>Door</t>
+  </si>
+  <si>
+    <t>no tax</t>
+  </si>
+  <si>
+    <t>ShirtProduct</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>TestBook</t>
+  </si>
+  <si>
+    <t>Dollar Discount</t>
+  </si>
+  <si>
+    <t>TC_11015</t>
+  </si>
+  <si>
+    <t>0005</t>
+  </si>
+  <si>
+    <t>Amex</t>
+  </si>
+  <si>
+    <t>CA - California</t>
+  </si>
+  <si>
+    <t>Rustic Rubber</t>
+  </si>
+  <si>
+    <t>MobilePhone</t>
+  </si>
+  <si>
+    <t>default tax rate</t>
+  </si>
+  <si>
+    <t>TC_11021</t>
+  </si>
+  <si>
+    <t>6/15 Zentro test for robert esa</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>umeshkumar@gmail.com</t>
+  </si>
+  <si>
+    <t>ACH/EFT</t>
+  </si>
+  <si>
+    <t>7244</t>
+  </si>
+  <si>
+    <t>1/11 colony</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>Blvd Founders</t>
+  </si>
+  <si>
+    <t>newdiscount</t>
+  </si>
+  <si>
+    <t>FruitProduct</t>
+  </si>
+  <si>
+    <t>TC_11037</t>
+  </si>
+  <si>
+    <t>QA FEE TEST</t>
+  </si>
+  <si>
+    <t>HenryRR@gmail.com</t>
+  </si>
+  <si>
+    <t>6011111111111117</t>
+  </si>
+  <si>
+    <t>discover</t>
+  </si>
+  <si>
+    <t>No Tax</t>
+  </si>
+  <si>
+    <t>TX - Texas</t>
+  </si>
+  <si>
+    <t>BuyDoor</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>TextBook</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>TC_11031</t>
+  </si>
+  <si>
+    <t>4012888888881881</t>
+  </si>
+  <si>
+    <t>visa</t>
+  </si>
+  <si>
+    <t>SemiAnnually</t>
+  </si>
+  <si>
     <t>ZENTRO PROD TEST</t>
   </si>
   <si>
-    <t>umesh</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>umeshtest@testingxperts.com</t>
-  </si>
-  <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>4444</t>
-  </si>
-  <si>
-    <t>Master</t>
-  </si>
-  <si>
-    <t>Door</t>
-  </si>
-  <si>
-    <t>no tax</t>
-  </si>
-  <si>
-    <t>ShirtProduct</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>TestBook</t>
-  </si>
-  <si>
-    <t>Dollar Discount</t>
-  </si>
-  <si>
-    <t>TC_11015</t>
-  </si>
-  <si>
-    <t>0005</t>
-  </si>
-  <si>
-    <t>Amex</t>
-  </si>
-  <si>
-    <t>Rustic Rubber</t>
-  </si>
-  <si>
-    <t>MobilePhone</t>
-  </si>
-  <si>
-    <t>default tax rate</t>
-  </si>
-  <si>
-    <t>TC_11021</t>
-  </si>
-  <si>
     <t>zentro test for robert esa</t>
-  </si>
-  <si>
-    <t>ACH/EFT</t>
-  </si>
-  <si>
-    <t>7244</t>
-  </si>
-  <si>
-    <t>1/11 colony</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>Blvd Founders</t>
-  </si>
-  <si>
-    <t>newdiscount</t>
-  </si>
-  <si>
-    <t>FruitProduct</t>
-  </si>
-  <si>
-    <t>TC_11037</t>
-  </si>
-  <si>
-    <t>QA FEE TEST</t>
-  </si>
-  <si>
-    <t>HenryRR@gmail.com</t>
-  </si>
-  <si>
-    <t>6011111111111117</t>
-  </si>
-  <si>
-    <t>discover</t>
-  </si>
-  <si>
-    <t>No Tax</t>
-  </si>
-  <si>
-    <t>TX - Texas</t>
-  </si>
-  <si>
-    <t>BuyDoor</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>TextBook</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>TC_11031</t>
-  </si>
-  <si>
-    <t>4012888888881881</t>
-  </si>
-  <si>
-    <t>visa</t>
-  </si>
-  <si>
-    <t>SemiAnnually</t>
   </si>
   <si>
     <t>TC_11032</t>
@@ -1222,7 +1243,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="14.8545454545455" customWidth="1"/>
@@ -1233,7 +1254,7 @@
     <col min="11" max="11" width="18.8545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1342,408 +1363,417 @@
       <c r="AJ1" t="s">
         <v>35</v>
       </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" ht="16" spans="1:26">
+    <row r="2" ht="16" spans="1:37">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2">
         <v>1222342342</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2">
         <v>444</v>
       </c>
       <c r="M2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P2">
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V2">
         <v>87686</v>
       </c>
       <c r="W2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="AK2">
+        <v>1117</v>
       </c>
     </row>
-    <row r="3" ht="16" spans="1:31">
+    <row r="3" ht="16" spans="1:37">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3">
         <v>1222342342</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L3">
         <v>444</v>
       </c>
       <c r="M3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3">
         <v>5</v>
       </c>
       <c r="Q3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="U3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V3">
         <v>87686</v>
       </c>
       <c r="W3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA3">
         <v>123456</v>
       </c>
       <c r="AB3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AC3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AD3">
         <v>5</v>
       </c>
       <c r="AE3" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="AK3">
+        <v>1117</v>
       </c>
     </row>
     <row r="4" ht="16" spans="1:36">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>1222342342</v>
+        <v>1232342345</v>
       </c>
       <c r="J4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="T4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="U4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="V4">
         <v>30606</v>
       </c>
       <c r="W4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AA4">
         <v>123456</v>
       </c>
       <c r="AJ4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="16" spans="1:35">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>50</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I5">
         <v>1231232345</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L5">
         <v>444</v>
       </c>
       <c r="M5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="S5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="T5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U5">
         <v>30606</v>
       </c>
       <c r="V5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="Z5">
         <v>12345</v>
       </c>
       <c r="AB5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AC5">
         <v>10</v>
       </c>
       <c r="AD5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="b">
         <v>1</v>
       </c>
       <c r="AH5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="16" spans="1:34">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I6">
         <v>1231232345</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L6">
         <v>444</v>
       </c>
       <c r="M6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O6">
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="S6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="T6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6">
         <v>30606</v>
       </c>
       <c r="V6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AG6" t="b">
         <v>1</v>
       </c>
       <c r="AH6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1871,242 +1901,242 @@
     </row>
     <row r="2" ht="16" spans="1:26">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2">
         <v>1222342342</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2">
         <v>444</v>
       </c>
       <c r="M2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P2">
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V2">
         <v>87686</v>
       </c>
       <c r="W2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" ht="16" spans="1:31">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3">
         <v>1222342342</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L3">
         <v>444</v>
       </c>
       <c r="M3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3">
         <v>5</v>
       </c>
       <c r="Q3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V3">
         <v>87686</v>
       </c>
       <c r="W3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA3">
         <v>123456</v>
       </c>
       <c r="AB3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AC3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AD3">
         <v>5</v>
       </c>
       <c r="AE3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="16" spans="1:36">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4">
         <v>1222342342</v>
       </c>
       <c r="J4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="T4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="U4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="V4">
         <v>30606</v>
       </c>
       <c r="W4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AA4">
         <v>123456</v>
       </c>
       <c r="AJ4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="16" spans="8:11">
@@ -2115,245 +2145,243 @@
     </row>
     <row r="6" ht="16" spans="1:35">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I6">
         <v>1231232345</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L6">
         <v>444</v>
       </c>
       <c r="M6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="S6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="T6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6">
         <v>30606</v>
       </c>
       <c r="V6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="Z6">
         <v>12345</v>
       </c>
       <c r="AB6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AC6">
         <v>10</v>
       </c>
       <c r="AD6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AG6" t="b">
         <v>1</v>
       </c>
       <c r="AH6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="16" spans="1:34">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I7">
         <v>1231232345</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L7">
         <v>444</v>
       </c>
       <c r="M7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7">
         <v>20</v>
       </c>
       <c r="P7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="S7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="T7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U7">
         <v>30606</v>
       </c>
       <c r="V7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AG7" t="b">
         <v>1</v>
       </c>
       <c r="AH7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="16" spans="8:11">
       <c r="H10" s="1"/>
-      <c r="I10"/>
-      <c r="J10"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11" ht="16" spans="1:32">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>50</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I11">
         <v>1231232345</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L11">
         <v>444</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O11">
         <v>50</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="S11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U11">
         <v>30606</v>
       </c>
       <c r="V11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="Z11">
         <v>12345</v>

--- a/TestData/DeluxeTestData.xlsx
+++ b/TestData/DeluxeTestData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="145">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -56,9 +56,6 @@
     <t>CardType</t>
   </si>
   <si>
-    <t>SelectCardType</t>
-  </si>
-  <si>
     <t>QuickSaleItemName</t>
   </si>
   <si>
@@ -119,190 +116,348 @@
     <t>Frequency</t>
   </si>
   <si>
+    <t>PresetSaleItem2</t>
+  </si>
+  <si>
+    <t>ExistNumber</t>
+  </si>
+  <si>
+    <t>AnnualMonth</t>
+  </si>
+  <si>
+    <t>AnnualOption</t>
+  </si>
+  <si>
+    <t>ShippingMethod</t>
+  </si>
+  <si>
+    <t>MID</t>
+  </si>
+  <si>
+    <t>CustomerFaxNumber</t>
+  </si>
+  <si>
+    <t>CardNumber1</t>
+  </si>
+  <si>
+    <t>CardExpiration1</t>
+  </si>
+  <si>
+    <t>CardNumber2</t>
+  </si>
+  <si>
+    <t>CardNumber3</t>
+  </si>
+  <si>
+    <t>CardNumber4</t>
+  </si>
+  <si>
+    <t>CardNumber5</t>
+  </si>
+  <si>
+    <t>CardExpiration2</t>
+  </si>
+  <si>
+    <t>CardExpiration3</t>
+  </si>
+  <si>
+    <t>CardExpiration4</t>
+  </si>
+  <si>
+    <t>CardExpiration5</t>
+  </si>
+  <si>
+    <t>AccountNickName</t>
+  </si>
+  <si>
+    <t>RoutingNumber</t>
+  </si>
+  <si>
+    <t>AccountNumber</t>
+  </si>
+  <si>
+    <t>AccountType</t>
+  </si>
+  <si>
+    <t>TC_11013</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>5/13 ZENTRO PROD TEST</t>
+  </si>
+  <si>
+    <t>umesh</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>umeshtest@testingxperts.com</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>4444</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>Door</t>
+  </si>
+  <si>
+    <t>no tax</t>
+  </si>
+  <si>
+    <t>ShirtProduct</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>TestBook</t>
+  </si>
+  <si>
+    <t>Dollar Discount</t>
+  </si>
+  <si>
+    <t>TC_11015</t>
+  </si>
+  <si>
+    <t>0005</t>
+  </si>
+  <si>
+    <t>Amex</t>
+  </si>
+  <si>
+    <t>Rustic Rubber</t>
+  </si>
+  <si>
+    <t>MobilePhone</t>
+  </si>
+  <si>
+    <t>default tax rate</t>
+  </si>
+  <si>
+    <t>TC_11021</t>
+  </si>
+  <si>
+    <t>6/15 Zentro test for robert esa</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>umeshkumar@gmail.com</t>
+  </si>
+  <si>
+    <t>ACH/EFT</t>
+  </si>
+  <si>
+    <t>7244</t>
+  </si>
+  <si>
+    <t>1/11 colony</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>Blvd Founders</t>
+  </si>
+  <si>
+    <t>newdiscount</t>
+  </si>
+  <si>
+    <t>FruitProduct</t>
+  </si>
+  <si>
+    <t>TC_11054</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Annually</t>
+    </r>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>5th</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>TC_11031</t>
+  </si>
+  <si>
+    <t>QA Fee Test</t>
+  </si>
+  <si>
+    <t>HenryRR@gmail.com</t>
+  </si>
+  <si>
+    <t>4012888888881881</t>
+  </si>
+  <si>
+    <t>visa</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>TX - Texas</t>
+  </si>
+  <si>
+    <t>BuyDoor</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>TC_11033</t>
+  </si>
+  <si>
+    <t>378282246310005</t>
+  </si>
+  <si>
+    <t>amex</t>
+  </si>
+  <si>
+    <t>BiWeekly</t>
+  </si>
+  <si>
+    <t>TC_11032</t>
+  </si>
+  <si>
+    <t>5555555555554444</t>
+  </si>
+  <si>
+    <t>master</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>TC_11037</t>
+  </si>
+  <si>
+    <t>6011111111111117</t>
+  </si>
+  <si>
+    <t>discover</t>
+  </si>
+  <si>
+    <t>No Tax</t>
+  </si>
+  <si>
+    <t>TextBook</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>TC_11038</t>
+  </si>
+  <si>
+    <t>SemiAnnually</t>
+  </si>
+  <si>
+    <t>TC_11011</t>
+  </si>
+  <si>
+    <t>IATS ZENTRO</t>
+  </si>
+  <si>
+    <t>(854) 584-5968</t>
+  </si>
+  <si>
+    <t>1881</t>
+  </si>
+  <si>
+    <t>Multiple cards</t>
+  </si>
+  <si>
+    <t>frugal finds</t>
+  </si>
+  <si>
+    <t>6280780007557770</t>
+  </si>
+  <si>
+    <t>(878) 585-8255</t>
+  </si>
+  <si>
+    <t>4012 8888 8888 1881</t>
+  </si>
+  <si>
+    <t>08 / 32</t>
+  </si>
+  <si>
+    <t>5555 5555 5555 4444</t>
+  </si>
+  <si>
+    <t>3782 822463 10005</t>
+  </si>
+  <si>
+    <t>6011 1111 1111 1117</t>
+  </si>
+  <si>
+    <t>3612 340985 3619</t>
+  </si>
+  <si>
+    <t>03 / 28</t>
+  </si>
+  <si>
+    <t>03 / 32</t>
+  </si>
+  <si>
+    <t>03 / 33</t>
+  </si>
+  <si>
+    <t>ACH account nickname</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
     <t>SwitchFrequency</t>
   </si>
   <si>
-    <t>PresetSaleItem2</t>
-  </si>
-  <si>
-    <t>ExistNumber</t>
-  </si>
-  <si>
-    <t>TC_11013</t>
-  </si>
-  <si>
-    <t>Sale</t>
-  </si>
-  <si>
-    <t>5/13 ZENTRO PROD TEST</t>
-  </si>
-  <si>
-    <t>umesh</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>umeshtest@testingxperts.com</t>
-  </si>
-  <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>4444</t>
-  </si>
-  <si>
-    <t>Master</t>
-  </si>
-  <si>
-    <t>Door</t>
-  </si>
-  <si>
-    <t>no tax</t>
-  </si>
-  <si>
-    <t>ShirtProduct</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>TestBook</t>
-  </si>
-  <si>
-    <t>Dollar Discount</t>
-  </si>
-  <si>
-    <t>TC_11015</t>
-  </si>
-  <si>
-    <t>0005</t>
-  </si>
-  <si>
-    <t>Amex</t>
-  </si>
-  <si>
     <t>CA - California</t>
   </si>
   <si>
-    <t>Rustic Rubber</t>
-  </si>
-  <si>
-    <t>MobilePhone</t>
-  </si>
-  <si>
-    <t>default tax rate</t>
-  </si>
-  <si>
-    <t>TC_11021</t>
-  </si>
-  <si>
-    <t>6/15 Zentro test for robert esa</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>customer</t>
-  </si>
-  <si>
-    <t>umeshkumar@gmail.com</t>
-  </si>
-  <si>
-    <t>ACH/EFT</t>
-  </si>
-  <si>
-    <t>7244</t>
-  </si>
-  <si>
-    <t>1/11 colony</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>Blvd Founders</t>
-  </si>
-  <si>
-    <t>newdiscount</t>
-  </si>
-  <si>
-    <t>FruitProduct</t>
-  </si>
-  <si>
-    <t>TC_11037</t>
-  </si>
-  <si>
     <t>QA FEE TEST</t>
   </si>
   <si>
-    <t>HenryRR@gmail.com</t>
-  </si>
-  <si>
-    <t>6011111111111117</t>
-  </si>
-  <si>
-    <t>discover</t>
-  </si>
-  <si>
-    <t>No Tax</t>
-  </si>
-  <si>
-    <t>TX - Texas</t>
-  </si>
-  <si>
-    <t>BuyDoor</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>TextBook</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>TC_11031</t>
-  </si>
-  <si>
-    <t>4012888888881881</t>
-  </si>
-  <si>
-    <t>visa</t>
-  </si>
-  <si>
-    <t>SemiAnnually</t>
-  </si>
-  <si>
-    <t>ZENTRO PROD TEST</t>
-  </si>
-  <si>
-    <t>zentro test for robert esa</t>
-  </si>
-  <si>
-    <t>TC_11032</t>
-  </si>
-  <si>
     <t>HenryRR</t>
   </si>
   <si>
     <t>Roj</t>
-  </si>
-  <si>
-    <t>5555555555554444</t>
   </si>
 </sst>
 </file>
@@ -315,7 +470,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +491,19 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF313131"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -793,137 +961,141 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1243,8 +1415,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
+  <dimension ref="A1:BB11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14.8545454545455" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1252,9 +1424,10 @@
     <col min="4" max="4" width="19.2818181818182" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="11" max="11" width="18.8545454545455" customWidth="1"/>
+    <col min="52" max="53" width="10.5454545454545"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:54">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1351,7 +1524,7 @@
       <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AH1" t="s">
@@ -1366,420 +1539,871 @@
       <c r="AK1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="2" ht="16" spans="1:37">
+    <row r="2" ht="16" spans="1:35">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I2">
         <v>1222342342</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="L2">
         <v>444</v>
       </c>
       <c r="M2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2">
+        <v>63</v>
+      </c>
+      <c r="O2">
         <v>5</v>
       </c>
+      <c r="P2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2">
+        <v>67</v>
+      </c>
+      <c r="U2">
         <v>87686</v>
       </c>
+      <c r="V2" t="s">
+        <v>68</v>
+      </c>
       <c r="W2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="X2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="Y2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK2">
+        <v>71</v>
+      </c>
+      <c r="AI2">
         <v>1117</v>
       </c>
     </row>
-    <row r="3" ht="16" spans="1:37">
+    <row r="3" ht="16" spans="1:35">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I3">
         <v>1222342342</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="L3">
         <v>444</v>
       </c>
       <c r="M3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3">
+        <v>63</v>
+      </c>
+      <c r="O3">
         <v>5</v>
       </c>
+      <c r="P3" t="s">
+        <v>64</v>
+      </c>
       <c r="Q3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="T3" t="s">
-        <v>58</v>
-      </c>
-      <c r="U3" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3">
+        <v>67</v>
+      </c>
+      <c r="U3">
         <v>87686</v>
       </c>
+      <c r="V3" t="s">
+        <v>68</v>
+      </c>
       <c r="W3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="X3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="Y3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA3">
+        <v>71</v>
+      </c>
+      <c r="Z3">
         <v>123456</v>
       </c>
+      <c r="AA3" t="s">
+        <v>75</v>
+      </c>
       <c r="AB3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD3">
+        <v>76</v>
+      </c>
+      <c r="AC3">
         <v>5</v>
       </c>
-      <c r="AE3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK3">
+      <c r="AD3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI3">
         <v>1117</v>
       </c>
     </row>
-    <row r="4" ht="16" spans="1:36">
+    <row r="4" ht="16" spans="1:34">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>1232342345</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" t="s">
+        <v>85</v>
+      </c>
+      <c r="S4" t="s">
+        <v>86</v>
+      </c>
+      <c r="T4" t="s">
+        <v>87</v>
+      </c>
+      <c r="U4">
+        <v>30606</v>
+      </c>
+      <c r="V4" t="s">
         <v>68</v>
       </c>
-      <c r="M4" t="s">
-        <v>67</v>
-      </c>
-      <c r="N4" t="s">
-        <v>67</v>
-      </c>
-      <c r="R4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="W4" t="s">
         <v>69</v>
       </c>
-      <c r="T4" t="s">
+      <c r="X4" t="s">
         <v>70</v>
       </c>
-      <c r="U4" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4">
-        <v>30606</v>
-      </c>
-      <c r="W4" t="s">
-        <v>51</v>
-      </c>
-      <c r="X4" t="s">
-        <v>52</v>
-      </c>
       <c r="Y4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA4">
+        <v>88</v>
+      </c>
+      <c r="Z4">
         <v>123456</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>73</v>
+      <c r="AH4" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="5" ht="16" spans="1:35">
+    <row r="5" ht="16" spans="1:38">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5">
-        <v>50</v>
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" t="s">
+        <v>81</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I5">
-        <v>1231232345</v>
+        <v>1232342345</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L5">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
       <c r="P5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="R5" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="S5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="T5" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="U5">
         <v>30606</v>
       </c>
       <c r="V5" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="W5" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="X5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="Y5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z5">
-        <v>12345</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC5">
-        <v>10</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="AE5">
+        <v>2</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="6" ht="16" spans="1:34">
+    <row r="6" ht="16" spans="1:33">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
+        <v>55</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I6">
         <v>1231232345</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="L6">
         <v>444</v>
       </c>
       <c r="M6" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="O6">
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="R6" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="S6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="T6" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="U6">
         <v>30606</v>
       </c>
       <c r="V6" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="W6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="X6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="Y6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" ht="16" spans="1:33">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7">
+        <v>1231232345</v>
+      </c>
+      <c r="J7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L7">
+        <v>444</v>
+      </c>
+      <c r="M7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O7">
+        <v>20</v>
+      </c>
+      <c r="P7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q7" t="s">
         <v>89</v>
+      </c>
+      <c r="R7" t="s">
+        <v>85</v>
+      </c>
+      <c r="S7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U7">
+        <v>30606</v>
+      </c>
+      <c r="V7" t="s">
+        <v>68</v>
+      </c>
+      <c r="W7" t="s">
+        <v>69</v>
+      </c>
+      <c r="X7" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" ht="16" spans="1:33">
+      <c r="A8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I8">
+        <v>1231232345</v>
+      </c>
+      <c r="J8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="L8">
+        <v>444</v>
+      </c>
+      <c r="M8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8">
+        <v>20</v>
+      </c>
+      <c r="P8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" t="s">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s">
+        <v>101</v>
+      </c>
+      <c r="T8" t="s">
+        <v>58</v>
+      </c>
+      <c r="U8">
+        <v>30606</v>
+      </c>
+      <c r="V8" t="s">
+        <v>68</v>
+      </c>
+      <c r="W8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X8" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE8">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" ht="16" spans="1:33">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9">
+        <v>1231232345</v>
+      </c>
+      <c r="J9" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>444</v>
+      </c>
+      <c r="M9" t="s">
+        <v>115</v>
+      </c>
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>89</v>
+      </c>
+      <c r="R9" t="s">
+        <v>85</v>
+      </c>
+      <c r="S9" t="s">
+        <v>101</v>
+      </c>
+      <c r="T9" t="s">
+        <v>58</v>
+      </c>
+      <c r="U9">
+        <v>30606</v>
+      </c>
+      <c r="V9" t="s">
+        <v>68</v>
+      </c>
+      <c r="W9" t="s">
+        <v>69</v>
+      </c>
+      <c r="X9" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z9">
+        <v>12345</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" ht="16" spans="1:33">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10">
+        <v>1231232345</v>
+      </c>
+      <c r="J10" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L10">
+        <v>444</v>
+      </c>
+      <c r="M10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O10">
+        <v>20</v>
+      </c>
+      <c r="P10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>89</v>
+      </c>
+      <c r="R10" t="s">
+        <v>85</v>
+      </c>
+      <c r="S10" t="s">
+        <v>101</v>
+      </c>
+      <c r="T10" t="s">
+        <v>58</v>
+      </c>
+      <c r="U10">
+        <v>30606</v>
+      </c>
+      <c r="V10" t="s">
+        <v>68</v>
+      </c>
+      <c r="W10" t="s">
+        <v>69</v>
+      </c>
+      <c r="X10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" ht="16" spans="1:54">
+      <c r="A11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N11" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>89</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" t="s">
+        <v>67</v>
+      </c>
+      <c r="U11">
+        <v>87686</v>
+      </c>
+      <c r="V11" t="s">
+        <v>68</v>
+      </c>
+      <c r="W11" t="s">
+        <v>69</v>
+      </c>
+      <c r="X11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z11">
+        <v>12345</v>
+      </c>
+      <c r="AI11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN11" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV11" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="AW11" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX11" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AZ11">
+        <v>123123123</v>
+      </c>
+      <c r="BA11">
+        <v>123456789</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H5" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
     <hyperlink ref="H6" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
+    <hyperlink ref="H7" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
+    <hyperlink ref="H8" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
+    <hyperlink ref="H9" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
+    <hyperlink ref="H10" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1795,7 +2419,7 @@
     <col min="9" max="9" width="14.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1836,54 +2460,57 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
       <c r="AF1" t="s">
@@ -1893,417 +2520,417 @@
         <v>32</v>
       </c>
       <c r="AH1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" ht="16" spans="1:26">
+    <row r="2" ht="16" spans="1:36">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I2">
         <v>1222342342</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="L2">
         <v>444</v>
       </c>
       <c r="M2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2">
+        <v>63</v>
+      </c>
+      <c r="O2">
         <v>5</v>
       </c>
+      <c r="P2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2">
+        <v>67</v>
+      </c>
+      <c r="U2">
         <v>87686</v>
       </c>
+      <c r="V2" t="s">
+        <v>68</v>
+      </c>
       <c r="W2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="X2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="Y2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>54</v>
+        <v>71</v>
+      </c>
+      <c r="AJ2">
+        <v>1117</v>
       </c>
     </row>
-    <row r="3" ht="16" spans="1:31">
+    <row r="3" ht="16" spans="1:36">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I3">
         <v>1222342342</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="L3">
         <v>444</v>
       </c>
       <c r="M3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3">
+        <v>63</v>
+      </c>
+      <c r="O3">
         <v>5</v>
       </c>
+      <c r="P3" t="s">
+        <v>64</v>
+      </c>
       <c r="Q3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
-      </c>
-      <c r="U3" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3">
+        <v>67</v>
+      </c>
+      <c r="U3">
         <v>87686</v>
       </c>
+      <c r="V3" t="s">
+        <v>68</v>
+      </c>
       <c r="W3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="X3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="Y3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA3">
+        <v>71</v>
+      </c>
+      <c r="Z3">
         <v>123456</v>
       </c>
+      <c r="AA3" t="s">
+        <v>75</v>
+      </c>
       <c r="AB3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD3">
+        <v>76</v>
+      </c>
+      <c r="AC3">
         <v>5</v>
       </c>
-      <c r="AE3" t="s">
-        <v>61</v>
+      <c r="AD3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ3">
+        <v>1117</v>
       </c>
     </row>
-    <row r="4" ht="16" spans="1:36">
+    <row r="4" ht="16" spans="1:35">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="I4">
-        <v>1222342342</v>
+        <v>1232342345</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" t="s">
+        <v>85</v>
+      </c>
+      <c r="S4" t="s">
+        <v>86</v>
+      </c>
+      <c r="T4" t="s">
+        <v>87</v>
+      </c>
+      <c r="U4">
+        <v>30606</v>
+      </c>
+      <c r="V4" t="s">
         <v>68</v>
       </c>
-      <c r="M4" t="s">
-        <v>67</v>
-      </c>
-      <c r="N4" t="s">
-        <v>67</v>
-      </c>
-      <c r="R4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="W4" t="s">
         <v>69</v>
       </c>
-      <c r="T4" t="s">
+      <c r="X4" t="s">
         <v>70</v>
       </c>
-      <c r="U4" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4">
-        <v>30606</v>
-      </c>
-      <c r="W4" t="s">
-        <v>51</v>
-      </c>
-      <c r="X4" t="s">
-        <v>52</v>
-      </c>
       <c r="Y4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA4">
+        <v>88</v>
+      </c>
+      <c r="Z4">
         <v>123456</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>73</v>
+      <c r="AI4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" ht="16" spans="8:11">
       <c r="H5" s="1"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" ht="16" spans="1:35">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6">
-        <v>1231232345</v>
-      </c>
-      <c r="J6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6">
-        <v>444</v>
-      </c>
-      <c r="M6" t="s">
-        <v>78</v>
-      </c>
-      <c r="N6" t="s">
-        <v>46</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
-      <c r="P6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" t="s">
-        <v>69</v>
-      </c>
-      <c r="S6" t="s">
-        <v>80</v>
-      </c>
-      <c r="T6" t="s">
-        <v>41</v>
-      </c>
-      <c r="U6">
-        <v>30606</v>
-      </c>
-      <c r="V6" t="s">
-        <v>51</v>
-      </c>
-      <c r="W6" t="s">
-        <v>52</v>
-      </c>
-      <c r="X6" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z6">
-        <v>12345</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC6">
-        <v>10</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>85</v>
-      </c>
-    </row>
     <row r="7" ht="16" spans="1:34">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="E7">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I7">
         <v>1231232345</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="L7">
         <v>444</v>
       </c>
       <c r="M7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="O7">
         <v>20</v>
       </c>
       <c r="P7" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="R7" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="S7" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="T7" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="U7">
         <v>30606</v>
       </c>
       <c r="V7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="W7" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="X7" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="Y7" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="b">
         <v>1</v>
       </c>
       <c r="AH7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" ht="16" spans="1:35">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I8">
+        <v>1231232345</v>
+      </c>
+      <c r="J8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L8">
+        <v>444</v>
+      </c>
+      <c r="M8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q8" t="s">
         <v>89</v>
+      </c>
+      <c r="R8" t="s">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s">
+        <v>101</v>
+      </c>
+      <c r="T8" t="s">
+        <v>58</v>
+      </c>
+      <c r="U8">
+        <v>30606</v>
+      </c>
+      <c r="V8" t="s">
+        <v>68</v>
+      </c>
+      <c r="W8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X8" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z8">
+        <v>12345</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC8">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10" ht="16" spans="8:11">
@@ -2312,76 +2939,76 @@
     </row>
     <row r="11" ht="16" spans="1:32">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="E11">
         <v>50</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I11">
         <v>1231232345</v>
       </c>
       <c r="J11" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="L11">
         <v>444</v>
       </c>
       <c r="M11" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="N11" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="O11">
         <v>50</v>
       </c>
       <c r="P11" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="R11" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="S11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="T11" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="U11">
         <v>30606</v>
       </c>
       <c r="V11" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="W11" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="X11" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="Y11" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="Z11">
         <v>12345</v>
@@ -2393,7 +3020,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H11" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
-    <hyperlink ref="H6" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
+    <hyperlink ref="H8" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
     <hyperlink ref="H7" r:id="rId1" display="HenryRR@gmail.com" tooltip="mailto:HenryRR@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
